--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403648</v>
+        <v>129410968</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559588</v>
+        <v>559550</v>
       </c>
       <c r="R5" t="n">
-        <v>7064187</v>
+        <v>7064192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,19 +1086,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410968</v>
+        <v>129410965</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559550</v>
+        <v>559293</v>
       </c>
       <c r="R6" t="n">
-        <v>7064192</v>
+        <v>7064263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410965</v>
+        <v>129403648</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559293</v>
+        <v>559588</v>
       </c>
       <c r="R7" t="n">
-        <v>7064263</v>
+        <v>7064187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,14 +1268,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,27 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R8" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,12 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,31 +1434,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R9" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1508,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129406164</v>
+        <v>129410970</v>
       </c>
       <c r="B10" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,26 +1568,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559539</v>
+        <v>559696</v>
       </c>
       <c r="R10" t="n">
-        <v>7064245</v>
+        <v>7064169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,19 +1608,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,19 +1630,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1685,21 +1671,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R11" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,24 +1710,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,19 +1732,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410970</v>
+        <v>129403237</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1802,16 +1773,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559696</v>
+        <v>559726</v>
       </c>
       <c r="R12" t="n">
-        <v>7064169</v>
+        <v>7064107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,14 +1817,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,39 +1849,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129410978</v>
+        <v>129406164</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1903,17 +1889,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559550</v>
+        <v>559539</v>
       </c>
       <c r="R13" t="n">
-        <v>7064229</v>
+        <v>7064245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,14 +1938,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,12 +1965,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129401816</v>
+        <v>129410975</v>
       </c>
       <c r="B24" t="n">
         <v>57727</v>
@@ -3086,21 +3086,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559686</v>
+        <v>559540</v>
       </c>
       <c r="R24" t="n">
-        <v>7064015</v>
+        <v>7064261</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,24 +3125,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,19 +3147,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129410975</v>
+        <v>129401816</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3203,16 +3188,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559540</v>
+        <v>559686</v>
       </c>
       <c r="R25" t="n">
-        <v>7064261</v>
+        <v>7064015</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,14 +3232,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3264,12 +3264,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R29" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R30" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129410976</v>
+        <v>129403742</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3894,16 +3894,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559547</v>
+        <v>559536</v>
       </c>
       <c r="R31" t="n">
-        <v>7064246</v>
+        <v>7064197</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,14 +3938,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3955,39 +3970,39 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129410995</v>
+        <v>129410976</v>
       </c>
       <c r="B32" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4002,10 +4017,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559567</v>
+        <v>559547</v>
       </c>
       <c r="R32" t="n">
-        <v>7064280</v>
+        <v>7064246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4038,6 +4053,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4064,27 +4084,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129403742</v>
+        <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4093,21 +4113,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559536</v>
+        <v>559567</v>
       </c>
       <c r="R33" t="n">
-        <v>7064197</v>
+        <v>7064280</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,24 +4152,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4169,19 +4169,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129404246</v>
+        <v>129410979</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4210,21 +4210,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>559534</v>
+        <v>559552</v>
       </c>
       <c r="R34" t="n">
-        <v>7064254</v>
+        <v>7064200</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4254,24 +4249,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4286,19 +4266,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129410979</v>
+        <v>129404246</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4327,16 +4307,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>559552</v>
+        <v>559534</v>
       </c>
       <c r="R35" t="n">
-        <v>7064200</v>
+        <v>7064254</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,9 +4351,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4383,12 +4383,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129410990</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129404077</v>
       </c>
       <c r="B4" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410965</v>
+        <v>129403648</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559293</v>
+        <v>559588</v>
       </c>
       <c r="R6" t="n">
-        <v>7064263</v>
+        <v>7064187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,14 +1166,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129403648</v>
+        <v>129410965</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559588</v>
+        <v>559293</v>
       </c>
       <c r="R7" t="n">
-        <v>7064187</v>
+        <v>7064263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,19 +1273,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
         <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129402745</v>
+        <v>129402837</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559641</v>
+        <v>559663</v>
       </c>
       <c r="R16" t="n">
-        <v>7064141</v>
+        <v>7064138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2313,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129402837</v>
+        <v>129411002</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,39 +2324,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559663</v>
+        <v>559393</v>
       </c>
       <c r="R17" t="n">
-        <v>7064138</v>
+        <v>7064264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,24 +2381,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2418,22 +2398,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129411002</v>
+        <v>129411003</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559393</v>
+        <v>559507</v>
       </c>
       <c r="R18" t="n">
-        <v>7064264</v>
+        <v>7064295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129411003</v>
+        <v>129402745</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,34 +2518,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559507</v>
+        <v>559641</v>
       </c>
       <c r="R19" t="n">
-        <v>7064295</v>
+        <v>7064141</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,9 +2580,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,12 +2612,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4398,7 +4398,7 @@
         <v>129410991</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>129410964</v>
       </c>
       <c r="B37" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>129410989</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,31 +1318,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1351,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R8" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1392,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,27 +1435,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R9" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1508,12 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R29" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R30" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129403742</v>
+        <v>129410995</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,21 +3894,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559536</v>
+        <v>559567</v>
       </c>
       <c r="R31" t="n">
-        <v>7064197</v>
+        <v>7064280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,24 +3933,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,19 +3950,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129410976</v>
+        <v>129403742</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -4011,16 +3991,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559547</v>
+        <v>559536</v>
       </c>
       <c r="R32" t="n">
-        <v>7064246</v>
+        <v>7064197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,14 +4035,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,39 +4067,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410995</v>
+        <v>129410976</v>
       </c>
       <c r="B33" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559567</v>
+        <v>559547</v>
       </c>
       <c r="R33" t="n">
-        <v>7064280</v>
+        <v>7064246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129410990</v>
       </c>
       <c r="B3" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129404077</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129410968</v>
+        <v>129403648</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559550</v>
+        <v>559588</v>
       </c>
       <c r="R5" t="n">
-        <v>7064192</v>
+        <v>7064187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,14 +1064,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129403648</v>
+        <v>129410968</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559588</v>
+        <v>559550</v>
       </c>
       <c r="R6" t="n">
-        <v>7064187</v>
+        <v>7064192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,19 +1171,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         <v>129404125</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129402837</v>
+        <v>129411003</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,39 +2207,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559663</v>
+        <v>559507</v>
       </c>
       <c r="R16" t="n">
-        <v>7064138</v>
+        <v>7064295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,24 +2264,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,12 +2281,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2316,7 +2296,7 @@
         <v>129411002</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129411003</v>
+        <v>129402745</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,34 +2401,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559507</v>
+        <v>559641</v>
       </c>
       <c r="R18" t="n">
-        <v>7064295</v>
+        <v>7064141</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,9 +2463,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2495,19 +2495,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129402745</v>
+        <v>129402837</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559641</v>
+        <v>559663</v>
       </c>
       <c r="R19" t="n">
-        <v>7064141</v>
+        <v>7064138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,36 +3287,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3325,13 +3316,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R26" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3360,7 +3351,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3361,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,27 +3404,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3437,13 +3442,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R27" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3472,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3482,12 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R29" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R30" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129410995</v>
+        <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,16 +3894,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559567</v>
+        <v>559536</v>
       </c>
       <c r="R31" t="n">
-        <v>7064280</v>
+        <v>7064197</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,9 +3938,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,19 +3970,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129403742</v>
+        <v>129410976</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3991,21 +4011,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559536</v>
+        <v>559547</v>
       </c>
       <c r="R32" t="n">
-        <v>7064197</v>
+        <v>7064246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,24 +4050,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,39 +4072,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410976</v>
+        <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559547</v>
+        <v>559567</v>
       </c>
       <c r="R33" t="n">
-        <v>7064246</v>
+        <v>7064280</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4398,7 +4398,7 @@
         <v>129410991</v>
       </c>
       <c r="B36" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>129410964</v>
       </c>
       <c r="B37" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>129410989</v>
       </c>
       <c r="B38" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,27 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R8" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,12 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,31 +1434,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R9" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1508,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410970</v>
+        <v>129406164</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,17 +1568,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559696</v>
+        <v>559539</v>
       </c>
       <c r="R10" t="n">
-        <v>7064169</v>
+        <v>7064245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,14 +1617,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,19 +1644,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410978</v>
+        <v>129410970</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1677,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559550</v>
+        <v>559696</v>
       </c>
       <c r="R11" t="n">
-        <v>7064229</v>
+        <v>7064169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1731,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1773,21 +1787,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R12" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,24 +1826,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,39 +1848,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406164</v>
+        <v>129403237</v>
       </c>
       <c r="B13" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1889,26 +1888,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559539</v>
+        <v>559726</v>
       </c>
       <c r="R13" t="n">
-        <v>7064245</v>
+        <v>7064107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1950,7 +1945,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2196,7 +2196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411003</v>
+        <v>129411002</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559507</v>
+        <v>559393</v>
       </c>
       <c r="R16" t="n">
-        <v>7064295</v>
+        <v>7064264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411002</v>
+        <v>129411003</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559393</v>
+        <v>559507</v>
       </c>
       <c r="R17" t="n">
-        <v>7064264</v>
+        <v>7064295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,27 +3287,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3316,13 +3325,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R26" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3351,7 +3360,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3361,12 +3370,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,10 +3397,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,36 +3408,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3442,13 +3437,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R27" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3477,7 +3472,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3482,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129403742</v>
+        <v>129410995</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,21 +3894,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559536</v>
+        <v>559567</v>
       </c>
       <c r="R31" t="n">
-        <v>7064197</v>
+        <v>7064280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,24 +3933,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,19 +3950,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129410976</v>
+        <v>129403742</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -4011,16 +3991,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559547</v>
+        <v>559536</v>
       </c>
       <c r="R32" t="n">
-        <v>7064246</v>
+        <v>7064197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,14 +4035,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,39 +4067,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410995</v>
+        <v>129410976</v>
       </c>
       <c r="B33" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559567</v>
+        <v>559547</v>
       </c>
       <c r="R33" t="n">
-        <v>7064280</v>
+        <v>7064246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403648</v>
+        <v>129410968</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559588</v>
+        <v>559550</v>
       </c>
       <c r="R5" t="n">
-        <v>7064187</v>
+        <v>7064192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,19 +1086,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410968</v>
+        <v>129410965</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559550</v>
+        <v>559293</v>
       </c>
       <c r="R6" t="n">
-        <v>7064192</v>
+        <v>7064263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410965</v>
+        <v>129403648</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559293</v>
+        <v>559588</v>
       </c>
       <c r="R7" t="n">
-        <v>7064263</v>
+        <v>7064187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,14 +1268,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B8" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,31 +1318,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1351,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R8" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1392,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,27 +1435,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R9" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1508,12 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410978</v>
+        <v>129403237</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1787,16 +1787,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559550</v>
+        <v>559726</v>
       </c>
       <c r="R12" t="n">
-        <v>7064229</v>
+        <v>7064107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,14 +1831,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,19 +1863,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1889,21 +1904,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R13" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,24 +1943,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,19 +1965,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403047</v>
+        <v>129410969</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2006,21 +2006,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559683</v>
+        <v>559580</v>
       </c>
       <c r="R14" t="n">
-        <v>7064133</v>
+        <v>7064207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,24 +2045,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,19 +2067,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410969</v>
+        <v>129403047</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2123,16 +2108,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559580</v>
+        <v>559683</v>
       </c>
       <c r="R15" t="n">
-        <v>7064207</v>
+        <v>7064133</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,14 +2152,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,12 +2184,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R20" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B21" t="n">
         <v>57727</v>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R21" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,36 +3287,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3325,13 +3316,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R26" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3360,7 +3351,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3361,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,27 +3404,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3437,13 +3442,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R27" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3472,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3482,12 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R29" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R30" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129410995</v>
+        <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,16 +3894,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559567</v>
+        <v>559536</v>
       </c>
       <c r="R31" t="n">
-        <v>7064280</v>
+        <v>7064197</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,9 +3938,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,19 +3970,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129403742</v>
+        <v>129410976</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3991,21 +4011,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559536</v>
+        <v>559547</v>
       </c>
       <c r="R32" t="n">
-        <v>7064197</v>
+        <v>7064246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,24 +4050,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,39 +4072,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410976</v>
+        <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559547</v>
+        <v>559567</v>
       </c>
       <c r="R33" t="n">
-        <v>7064246</v>
+        <v>7064280</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,27 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R8" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,12 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,31 +1434,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R9" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1508,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129406164</v>
+        <v>129410970</v>
       </c>
       <c r="B10" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,26 +1568,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559539</v>
+        <v>559696</v>
       </c>
       <c r="R10" t="n">
-        <v>7064245</v>
+        <v>7064169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,19 +1608,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,19 +1630,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410970</v>
+        <v>129410978</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1691,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559696</v>
+        <v>559550</v>
       </c>
       <c r="R11" t="n">
-        <v>7064169</v>
+        <v>7064229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1717,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,27 +1861,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129410978</v>
+        <v>129406164</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1903,17 +1889,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559550</v>
+        <v>559539</v>
       </c>
       <c r="R13" t="n">
-        <v>7064229</v>
+        <v>7064245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,14 +1938,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,12 +1965,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R20" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B21" t="n">
         <v>57727</v>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R21" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129403742</v>
+        <v>129410995</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,21 +3894,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559536</v>
+        <v>559567</v>
       </c>
       <c r="R31" t="n">
-        <v>7064197</v>
+        <v>7064280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,24 +3933,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,19 +3950,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129410976</v>
+        <v>129403742</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -4011,16 +3991,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559547</v>
+        <v>559536</v>
       </c>
       <c r="R32" t="n">
-        <v>7064246</v>
+        <v>7064197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,14 +4035,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,39 +4067,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410995</v>
+        <v>129410976</v>
       </c>
       <c r="B33" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559567</v>
+        <v>559547</v>
       </c>
       <c r="R33" t="n">
-        <v>7064280</v>
+        <v>7064246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129410968</v>
+        <v>129403648</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559550</v>
+        <v>559588</v>
       </c>
       <c r="R5" t="n">
-        <v>7064192</v>
+        <v>7064187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,14 +1064,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410965</v>
+        <v>129410968</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559293</v>
+        <v>559550</v>
       </c>
       <c r="R6" t="n">
-        <v>7064263</v>
+        <v>7064192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129403648</v>
+        <v>129410965</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559588</v>
+        <v>559293</v>
       </c>
       <c r="R7" t="n">
-        <v>7064187</v>
+        <v>7064263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,19 +1273,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,31 +1318,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1351,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R8" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1392,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,27 +1435,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R9" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1508,12 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410970</v>
+        <v>129406164</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,17 +1568,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559696</v>
+        <v>559539</v>
       </c>
       <c r="R10" t="n">
-        <v>7064169</v>
+        <v>7064245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,14 +1617,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,19 +1644,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410978</v>
+        <v>129410970</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1677,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559550</v>
+        <v>559696</v>
       </c>
       <c r="R11" t="n">
-        <v>7064229</v>
+        <v>7064169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1731,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1773,21 +1787,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R12" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,24 +1826,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,39 +1848,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406164</v>
+        <v>129403237</v>
       </c>
       <c r="B13" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1889,26 +1888,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559539</v>
+        <v>559726</v>
       </c>
       <c r="R13" t="n">
-        <v>7064245</v>
+        <v>7064107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1950,7 +1945,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -4684,6 +4684,531 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129554412</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>559681</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7064349</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129555537</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>559771</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7064292</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129554321</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>559681</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7064349</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129554691</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>559654</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7064439</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129555462</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90932</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>559729</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7064224</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -1427,7 +1427,7 @@
         <v>129404125</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129406164</v>
+        <v>129410970</v>
       </c>
       <c r="B10" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,26 +1568,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559539</v>
+        <v>559696</v>
       </c>
       <c r="R10" t="n">
-        <v>7064245</v>
+        <v>7064169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,19 +1608,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,19 +1630,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410970</v>
+        <v>129403237</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1685,16 +1671,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559696</v>
+        <v>559726</v>
       </c>
       <c r="R11" t="n">
-        <v>7064169</v>
+        <v>7064107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,14 +1715,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,12 +1747,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1860,27 +1861,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403237</v>
+        <v>129406164</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1888,22 +1889,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559726</v>
+        <v>559539</v>
       </c>
       <c r="R13" t="n">
-        <v>7064107</v>
+        <v>7064245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1940,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,12 +1950,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2390,7 +2390,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129402745</v>
+        <v>129402837</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559641</v>
+        <v>559663</v>
       </c>
       <c r="R18" t="n">
-        <v>7064141</v>
+        <v>7064138</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2507,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129402837</v>
+        <v>129402745</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559663</v>
+        <v>559641</v>
       </c>
       <c r="R19" t="n">
-        <v>7064138</v>
+        <v>7064141</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R20" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B21" t="n">
         <v>57727</v>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R21" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,27 +3287,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3316,13 +3325,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R26" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3351,7 +3360,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3361,12 +3370,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,10 +3397,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,36 +3408,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3442,13 +3437,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R27" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3477,7 +3472,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3482,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,37 +4906,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R41" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4965,7 +4970,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4975,7 +4980,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,42 +5018,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R42" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5117,7 @@
         <v>129555462</v>
       </c>
       <c r="B43" t="n">
-        <v>90932</v>
+        <v>90935</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403648</v>
+        <v>129410965</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559588</v>
+        <v>559293</v>
       </c>
       <c r="R5" t="n">
-        <v>7064187</v>
+        <v>7064263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410968</v>
+        <v>129403648</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559550</v>
+        <v>559588</v>
       </c>
       <c r="R6" t="n">
-        <v>7064192</v>
+        <v>7064187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,14 +1166,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,19 +1193,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410965</v>
+        <v>129410968</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559293</v>
+        <v>559550</v>
       </c>
       <c r="R7" t="n">
-        <v>7064263</v>
+        <v>7064192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,27 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R8" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,12 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B9" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,31 +1434,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R9" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1508,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,7 +1642,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1671,21 +1671,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R11" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,24 +1710,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,19 +1732,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410978</v>
+        <v>129403237</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1788,16 +1773,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559550</v>
+        <v>559726</v>
       </c>
       <c r="R12" t="n">
-        <v>7064229</v>
+        <v>7064107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,14 +1817,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,12 +1849,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129410969</v>
+        <v>129403047</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2006,16 +2006,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559580</v>
+        <v>559683</v>
       </c>
       <c r="R14" t="n">
-        <v>7064207</v>
+        <v>7064133</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,14 +2050,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,19 +2082,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129403047</v>
+        <v>129410969</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2108,21 +2123,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559683</v>
+        <v>559580</v>
       </c>
       <c r="R15" t="n">
-        <v>7064133</v>
+        <v>7064207</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,24 +2162,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,12 +2184,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129402837</v>
+        <v>129402745</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559663</v>
+        <v>559641</v>
       </c>
       <c r="R18" t="n">
-        <v>7064138</v>
+        <v>7064141</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2507,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129402745</v>
+        <v>129402837</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559641</v>
+        <v>559663</v>
       </c>
       <c r="R19" t="n">
-        <v>7064141</v>
+        <v>7064138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R20" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B21" t="n">
         <v>57727</v>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R21" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,36 +3287,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3325,13 +3316,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R26" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3360,7 +3351,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3361,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,27 +3404,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3437,13 +3442,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R27" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3472,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3482,12 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R29" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R30" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129410995</v>
+        <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,16 +3894,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559567</v>
+        <v>559536</v>
       </c>
       <c r="R31" t="n">
-        <v>7064280</v>
+        <v>7064197</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,9 +3938,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,19 +3970,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129403742</v>
+        <v>129410976</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3991,21 +4011,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559536</v>
+        <v>559547</v>
       </c>
       <c r="R32" t="n">
-        <v>7064197</v>
+        <v>7064246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,24 +4050,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,39 +4072,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410976</v>
+        <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559547</v>
+        <v>559567</v>
       </c>
       <c r="R33" t="n">
-        <v>7064246</v>
+        <v>7064280</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,42 +4906,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R41" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4970,7 +4965,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4980,7 +4975,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5007,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,37 +5013,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R42" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129410965</v>
+        <v>129410968</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559293</v>
+        <v>559550</v>
       </c>
       <c r="R5" t="n">
-        <v>7064263</v>
+        <v>7064192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129403648</v>
+        <v>129410965</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559588</v>
+        <v>559293</v>
       </c>
       <c r="R6" t="n">
-        <v>7064187</v>
+        <v>7064263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,19 +1166,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410968</v>
+        <v>129403648</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559550</v>
+        <v>559588</v>
       </c>
       <c r="R7" t="n">
-        <v>7064192</v>
+        <v>7064187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,14 +1268,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410970</v>
+        <v>129406164</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,17 +1568,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559696</v>
+        <v>559539</v>
       </c>
       <c r="R10" t="n">
-        <v>7064169</v>
+        <v>7064245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,14 +1617,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,19 +1644,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410978</v>
+        <v>129410970</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1677,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559550</v>
+        <v>559696</v>
       </c>
       <c r="R11" t="n">
-        <v>7064229</v>
+        <v>7064169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1731,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1773,21 +1787,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R12" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,24 +1826,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,39 +1848,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406164</v>
+        <v>129403237</v>
       </c>
       <c r="B13" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1889,26 +1888,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559539</v>
+        <v>559726</v>
       </c>
       <c r="R13" t="n">
-        <v>7064245</v>
+        <v>7064107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1950,7 +1945,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129410968</v>
+        <v>129403648</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559550</v>
+        <v>559588</v>
       </c>
       <c r="R5" t="n">
-        <v>7064192</v>
+        <v>7064187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,14 +1064,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410965</v>
+        <v>129410968</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559293</v>
+        <v>559550</v>
       </c>
       <c r="R6" t="n">
-        <v>7064263</v>
+        <v>7064192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129403648</v>
+        <v>129410965</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559588</v>
+        <v>559293</v>
       </c>
       <c r="R7" t="n">
-        <v>7064187</v>
+        <v>7064263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,19 +1273,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,27 +3287,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3316,13 +3325,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R26" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3351,7 +3360,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3361,12 +3370,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,10 +3397,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,36 +3408,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3442,13 +3437,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R27" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3477,7 +3472,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3482,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129403742</v>
+        <v>129410995</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,21 +3894,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559536</v>
+        <v>559567</v>
       </c>
       <c r="R31" t="n">
-        <v>7064197</v>
+        <v>7064280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,24 +3933,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,19 +3950,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129410976</v>
+        <v>129403742</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -4011,16 +3991,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559547</v>
+        <v>559536</v>
       </c>
       <c r="R32" t="n">
-        <v>7064246</v>
+        <v>7064197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,14 +4035,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,39 +4067,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410995</v>
+        <v>129410976</v>
       </c>
       <c r="B33" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559567</v>
+        <v>559547</v>
       </c>
       <c r="R33" t="n">
-        <v>7064280</v>
+        <v>7064246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,37 +4906,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R41" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4965,7 +4970,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4975,7 +4980,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,42 +5018,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R42" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403648</v>
+        <v>129410968</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559588</v>
+        <v>559550</v>
       </c>
       <c r="R5" t="n">
-        <v>7064187</v>
+        <v>7064192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,19 +1086,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410968</v>
+        <v>129410965</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559550</v>
+        <v>559293</v>
       </c>
       <c r="R6" t="n">
-        <v>7064192</v>
+        <v>7064263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410965</v>
+        <v>129403648</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559293</v>
+        <v>559588</v>
       </c>
       <c r="R7" t="n">
-        <v>7064263</v>
+        <v>7064187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,14 +1268,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B8" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,31 +1318,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1351,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R8" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1392,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,27 +1435,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R9" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1508,12 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410978</v>
+        <v>129403237</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1787,16 +1787,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559550</v>
+        <v>559726</v>
       </c>
       <c r="R12" t="n">
-        <v>7064229</v>
+        <v>7064107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,14 +1831,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,19 +1863,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1889,21 +1904,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R13" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,24 +1943,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,19 +1965,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403047</v>
+        <v>129410969</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2006,21 +2006,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559683</v>
+        <v>559580</v>
       </c>
       <c r="R14" t="n">
-        <v>7064133</v>
+        <v>7064207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,24 +2045,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,19 +2067,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410969</v>
+        <v>129403047</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2123,16 +2108,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559580</v>
+        <v>559683</v>
       </c>
       <c r="R15" t="n">
-        <v>7064207</v>
+        <v>7064133</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,14 +2152,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,12 +2184,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R20" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B21" t="n">
         <v>57727</v>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R21" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,36 +3287,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3325,13 +3316,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R26" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3360,7 +3351,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3361,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,27 +3404,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3437,13 +3442,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R27" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3472,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3482,12 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R29" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R30" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129410995</v>
+        <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,16 +3894,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559567</v>
+        <v>559536</v>
       </c>
       <c r="R31" t="n">
-        <v>7064280</v>
+        <v>7064197</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,9 +3938,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,19 +3970,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129403742</v>
+        <v>129410976</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3991,21 +4011,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559536</v>
+        <v>559547</v>
       </c>
       <c r="R32" t="n">
-        <v>7064197</v>
+        <v>7064246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,24 +4050,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,39 +4072,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410976</v>
+        <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559547</v>
+        <v>559567</v>
       </c>
       <c r="R33" t="n">
-        <v>7064246</v>
+        <v>7064280</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129410968</v>
+        <v>129403648</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559550</v>
+        <v>559588</v>
       </c>
       <c r="R5" t="n">
-        <v>7064192</v>
+        <v>7064187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,14 +1064,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410965</v>
+        <v>129410968</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559293</v>
+        <v>559550</v>
       </c>
       <c r="R6" t="n">
-        <v>7064263</v>
+        <v>7064192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129403648</v>
+        <v>129410965</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559588</v>
+        <v>559293</v>
       </c>
       <c r="R7" t="n">
-        <v>7064187</v>
+        <v>7064263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,19 +1273,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129406164</v>
+        <v>129410978</v>
       </c>
       <c r="B10" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,26 +1568,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559539</v>
+        <v>559550</v>
       </c>
       <c r="R10" t="n">
-        <v>7064245</v>
+        <v>7064229</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,19 +1608,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,12 +1630,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1875,27 +1861,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129410978</v>
+        <v>129406164</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1903,17 +1889,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559550</v>
+        <v>559539</v>
       </c>
       <c r="R13" t="n">
-        <v>7064229</v>
+        <v>7064245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,14 +1938,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,12 +1965,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129402745</v>
+        <v>129402837</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559641</v>
+        <v>559663</v>
       </c>
       <c r="R18" t="n">
-        <v>7064141</v>
+        <v>7064138</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2507,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129402837</v>
+        <v>129402745</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559663</v>
+        <v>559641</v>
       </c>
       <c r="R19" t="n">
-        <v>7064138</v>
+        <v>7064141</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3057,7 +3057,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129410975</v>
+        <v>129401816</v>
       </c>
       <c r="B24" t="n">
         <v>57727</v>
@@ -3086,16 +3086,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559540</v>
+        <v>559686</v>
       </c>
       <c r="R24" t="n">
-        <v>7064261</v>
+        <v>7064015</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,14 +3130,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3147,19 +3162,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129401816</v>
+        <v>129410975</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3188,21 +3203,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559686</v>
+        <v>559540</v>
       </c>
       <c r="R25" t="n">
-        <v>7064015</v>
+        <v>7064261</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,24 +3242,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3264,12 +3264,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129403802</v>
+        <v>129404226</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559558</v>
+        <v>559526</v>
       </c>
       <c r="R28" t="n">
-        <v>7064251</v>
+        <v>7064261</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129403188</v>
+        <v>129403802</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559711</v>
+        <v>559558</v>
       </c>
       <c r="R29" t="n">
-        <v>7064112</v>
+        <v>7064251</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R30" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,42 +4906,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R41" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4970,7 +4965,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4980,7 +4975,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5007,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,37 +5013,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R42" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402787</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129410990</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129404077</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129403648</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129410968</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129410965</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,27 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R8" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,12 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B9" t="n">
-        <v>91851</v>
+        <v>57730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,31 +1434,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R9" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1508,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410978</v>
+        <v>129410970</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559550</v>
+        <v>559696</v>
       </c>
       <c r="R10" t="n">
-        <v>7064229</v>
+        <v>7064169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410970</v>
+        <v>129410978</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559696</v>
+        <v>559550</v>
       </c>
       <c r="R11" t="n">
-        <v>7064169</v>
+        <v>7064229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,7 +1747,7 @@
         <v>129403237</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>129406164</v>
       </c>
       <c r="B13" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129410969</v>
+        <v>129403047</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,16 +2006,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559580</v>
+        <v>559683</v>
       </c>
       <c r="R14" t="n">
-        <v>7064207</v>
+        <v>7064133</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,14 +2050,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,22 +2082,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129403047</v>
+        <v>129410969</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,21 +2123,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559683</v>
+        <v>559580</v>
       </c>
       <c r="R15" t="n">
-        <v>7064133</v>
+        <v>7064207</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,24 +2162,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,12 +2184,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
         <v>129411002</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129411003</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129402837</v>
+        <v>129402745</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559663</v>
+        <v>559641</v>
       </c>
       <c r="R18" t="n">
-        <v>7064138</v>
+        <v>7064141</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2507,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129402745</v>
+        <v>129402837</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559641</v>
+        <v>559663</v>
       </c>
       <c r="R19" t="n">
-        <v>7064141</v>
+        <v>7064138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2624,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R20" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R21" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410963</v>
+        <v>129410977</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559782</v>
+        <v>559545</v>
       </c>
       <c r="R22" t="n">
-        <v>7064120</v>
+        <v>7064246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410977</v>
+        <v>129410963</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2966,16 +2971,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2990,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559545</v>
+        <v>559782</v>
       </c>
       <c r="R23" t="n">
-        <v>7064246</v>
+        <v>7064120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,11 +3031,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129401816</v>
+        <v>129410975</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,21 +3086,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559686</v>
+        <v>559540</v>
       </c>
       <c r="R24" t="n">
-        <v>7064015</v>
+        <v>7064261</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,24 +3125,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,22 +3147,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129410975</v>
+        <v>129401816</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,16 +3188,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559540</v>
+        <v>559686</v>
       </c>
       <c r="R25" t="n">
-        <v>7064261</v>
+        <v>7064015</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,14 +3232,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3264,12 +3264,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
         <v>129402563</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129402806</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129404226</v>
+        <v>129403802</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559526</v>
+        <v>559558</v>
       </c>
       <c r="R28" t="n">
-        <v>7064261</v>
+        <v>7064251</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129403802</v>
+        <v>129404226</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559558</v>
+        <v>559526</v>
       </c>
       <c r="R29" t="n">
-        <v>7064251</v>
+        <v>7064261</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3751,7 +3751,7 @@
         <v>129403188</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129410976</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>129410979</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129404246</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>129410991</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4492,32 +4492,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129410964</v>
+        <v>129410989</v>
       </c>
       <c r="B37" t="n">
-        <v>80053</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559362</v>
+        <v>559357</v>
       </c>
       <c r="R37" t="n">
-        <v>7064266</v>
+        <v>7064264</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4589,32 +4589,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129410989</v>
+        <v>129410964</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>80079</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559357</v>
+        <v>559362</v>
       </c>
       <c r="R38" t="n">
-        <v>7064264</v>
+        <v>7064266</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4689,7 +4689,7 @@
         <v>129554412</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>129555537</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,37 +4906,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R41" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4965,7 +4970,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4975,7 +4980,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,42 +5018,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R42" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5117,7 @@
         <v>129555462</v>
       </c>
       <c r="B43" t="n">
-        <v>90935</v>
+        <v>90963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410970</v>
+        <v>129406164</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,17 +1568,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559696</v>
+        <v>559539</v>
       </c>
       <c r="R10" t="n">
-        <v>7064169</v>
+        <v>7064245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,14 +1617,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,19 +1644,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410978</v>
+        <v>129410970</v>
       </c>
       <c r="B11" t="n">
         <v>57730</v>
@@ -1677,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559550</v>
+        <v>559696</v>
       </c>
       <c r="R11" t="n">
-        <v>7064229</v>
+        <v>7064169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1731,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B12" t="n">
         <v>57730</v>
@@ -1773,21 +1787,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R12" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,24 +1826,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,39 +1848,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406164</v>
+        <v>129403237</v>
       </c>
       <c r="B13" t="n">
-        <v>57834</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1889,26 +1888,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559539</v>
+        <v>559726</v>
       </c>
       <c r="R13" t="n">
-        <v>7064245</v>
+        <v>7064107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1950,7 +1945,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B29" t="n">
         <v>57730</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R29" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B30" t="n">
         <v>57730</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R30" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4492,32 +4492,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129410989</v>
+        <v>129410964</v>
       </c>
       <c r="B37" t="n">
-        <v>80175</v>
+        <v>80079</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559357</v>
+        <v>559362</v>
       </c>
       <c r="R37" t="n">
-        <v>7064264</v>
+        <v>7064266</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4589,32 +4589,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129410964</v>
+        <v>129410989</v>
       </c>
       <c r="B38" t="n">
-        <v>80079</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559362</v>
+        <v>559357</v>
       </c>
       <c r="R38" t="n">
-        <v>7064266</v>
+        <v>7064264</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,42 +4906,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R41" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4970,7 +4965,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4980,7 +4975,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5007,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B42" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,37 +5013,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R42" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402787</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129410990</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129404077</v>
       </c>
       <c r="B4" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403648</v>
+        <v>129410968</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559588</v>
+        <v>559550</v>
       </c>
       <c r="R5" t="n">
-        <v>7064187</v>
+        <v>7064192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410968</v>
+        <v>129410965</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559550</v>
+        <v>559293</v>
       </c>
       <c r="R6" t="n">
-        <v>7064192</v>
+        <v>7064263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410965</v>
+        <v>129403648</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559293</v>
+        <v>559588</v>
       </c>
       <c r="R7" t="n">
-        <v>7064263</v>
+        <v>7064187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,14 +1268,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
         <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129404504</v>
       </c>
       <c r="B9" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>129406164</v>
       </c>
       <c r="B10" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>129410970</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>129410978</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>129403237</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129403047</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>129410969</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>129411002</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129411003</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>129402745</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>129402837</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>129401699</v>
       </c>
       <c r="B20" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>129402491</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410977</v>
+        <v>129410963</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>57732</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559545</v>
+        <v>559782</v>
       </c>
       <c r="R22" t="n">
-        <v>7064246</v>
+        <v>7064120</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,11 +2929,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410963</v>
+        <v>129410977</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2971,16 +2966,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2995,10 +2990,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559782</v>
+        <v>559545</v>
       </c>
       <c r="R23" t="n">
-        <v>7064120</v>
+        <v>7064246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,6 +3026,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3060,7 @@
         <v>129410975</v>
       </c>
       <c r="B24" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>129401816</v>
       </c>
       <c r="B25" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>129402563</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129402806</v>
       </c>
       <c r="B27" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>129403802</v>
       </c>
       <c r="B28" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B29" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R29" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R30" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,7 +3868,7 @@
         <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129410976</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>129410979</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129404246</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>129410991</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>129410964</v>
       </c>
       <c r="B37" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>129410989</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>129554412</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>129555537</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,37 +4906,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R41" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4965,7 +4970,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4975,7 +4980,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,42 +5018,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R42" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5117,7 @@
         <v>129555462</v>
       </c>
       <c r="B43" t="n">
-        <v>90963</v>
+        <v>90969</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402787</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129410990</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129404077</v>
       </c>
       <c r="B4" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129410968</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>129410965</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129403648</v>
       </c>
       <c r="B7" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129404504</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129406164</v>
+        <v>129410970</v>
       </c>
       <c r="B10" t="n">
-        <v>57839</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,26 +1568,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559539</v>
+        <v>559696</v>
       </c>
       <c r="R10" t="n">
-        <v>7064245</v>
+        <v>7064169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,19 +1608,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,22 +1630,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410970</v>
+        <v>129410978</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559696</v>
+        <v>559550</v>
       </c>
       <c r="R11" t="n">
-        <v>7064169</v>
+        <v>7064229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1717,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410978</v>
+        <v>129403237</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,16 +1773,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559550</v>
+        <v>559726</v>
       </c>
       <c r="R12" t="n">
-        <v>7064229</v>
+        <v>7064107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,14 +1817,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,39 +1849,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403237</v>
+        <v>129406164</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1888,22 +1889,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559726</v>
+        <v>559539</v>
       </c>
       <c r="R13" t="n">
-        <v>7064107</v>
+        <v>7064245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1940,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,12 +1950,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,7 +1980,7 @@
         <v>129403047</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>129410969</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>129411002</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411003</v>
+        <v>129402745</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,34 +2304,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559507</v>
+        <v>559641</v>
       </c>
       <c r="R17" t="n">
-        <v>7064295</v>
+        <v>7064141</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,9 +2366,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,22 +2398,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129402745</v>
+        <v>129402837</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559641</v>
+        <v>559663</v>
       </c>
       <c r="R18" t="n">
-        <v>7064141</v>
+        <v>7064138</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2485,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2475,7 +2495,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2507,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129402837</v>
+        <v>129411003</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,39 +2538,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559663</v>
+        <v>559507</v>
       </c>
       <c r="R19" t="n">
-        <v>7064138</v>
+        <v>7064295</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,24 +2595,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,12 +2612,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2627,7 +2627,7 @@
         <v>129401699</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>129402491</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>129410963</v>
       </c>
       <c r="B22" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>129410977</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>129410975</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>129401816</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>129402563</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129402806</v>
       </c>
       <c r="B27" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>129403802</v>
       </c>
       <c r="B28" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>129404226</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>129403188</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129410976</v>
       </c>
       <c r="B32" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>129410979</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129404246</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>129410991</v>
       </c>
       <c r="B36" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>129410964</v>
       </c>
       <c r="B37" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>129410989</v>
       </c>
       <c r="B38" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>129554412</v>
       </c>
       <c r="B39" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>129555537</v>
       </c>
       <c r="B40" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B41" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,42 +4906,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R41" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4970,7 +4965,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4980,7 +4975,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5007,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,37 +5013,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R42" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5117,7 @@
         <v>129555462</v>
       </c>
       <c r="B43" t="n">
-        <v>90969</v>
+        <v>90970</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129410968</v>
+        <v>129403648</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559550</v>
+        <v>559588</v>
       </c>
       <c r="R5" t="n">
-        <v>7064192</v>
+        <v>7064187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,14 +1064,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410965</v>
+        <v>129410968</v>
       </c>
       <c r="B6" t="n">
         <v>57736</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559293</v>
+        <v>559550</v>
       </c>
       <c r="R6" t="n">
-        <v>7064263</v>
+        <v>7064192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129403648</v>
+        <v>129410965</v>
       </c>
       <c r="B7" t="n">
-        <v>80181</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559588</v>
+        <v>559293</v>
       </c>
       <c r="R7" t="n">
-        <v>7064187</v>
+        <v>7064263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,19 +1273,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411002</v>
+        <v>129411003</v>
       </c>
       <c r="B16" t="n">
         <v>79076</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559393</v>
+        <v>559507</v>
       </c>
       <c r="R16" t="n">
-        <v>7064264</v>
+        <v>7064295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129411003</v>
+        <v>129411002</v>
       </c>
       <c r="B19" t="n">
         <v>79076</v>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559507</v>
+        <v>559393</v>
       </c>
       <c r="R19" t="n">
-        <v>7064295</v>
+        <v>7064264</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410963</v>
+        <v>129410977</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559782</v>
+        <v>559545</v>
       </c>
       <c r="R22" t="n">
-        <v>7064120</v>
+        <v>7064246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410977</v>
+        <v>129410963</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,16 +2971,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2990,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559545</v>
+        <v>559782</v>
       </c>
       <c r="R23" t="n">
-        <v>7064246</v>
+        <v>7064120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,11 +3031,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129410990</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129404077</v>
       </c>
       <c r="B4" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129403648</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411003</v>
+        <v>129411002</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559507</v>
+        <v>559393</v>
       </c>
       <c r="R16" t="n">
-        <v>7064295</v>
+        <v>7064264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129402745</v>
+        <v>129411003</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,39 +2304,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559641</v>
+        <v>559507</v>
       </c>
       <c r="R17" t="n">
-        <v>7064141</v>
+        <v>7064295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,24 +2361,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,19 +2378,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129402837</v>
+        <v>129402745</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2450,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559663</v>
+        <v>559641</v>
       </c>
       <c r="R18" t="n">
-        <v>7064138</v>
+        <v>7064141</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2495,7 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2527,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129411002</v>
+        <v>129402837</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,34 +2518,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559393</v>
+        <v>559663</v>
       </c>
       <c r="R19" t="n">
-        <v>7064264</v>
+        <v>7064138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,9 +2580,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,12 +2612,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410977</v>
+        <v>129410963</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559545</v>
+        <v>559782</v>
       </c>
       <c r="R22" t="n">
-        <v>7064246</v>
+        <v>7064120</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,11 +2929,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410963</v>
+        <v>129410977</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2971,16 +2966,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2995,10 +2990,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559782</v>
+        <v>559545</v>
       </c>
       <c r="R23" t="n">
-        <v>7064120</v>
+        <v>7064246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,6 +3026,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3514,7 +3514,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129403802</v>
+        <v>129403188</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3550,14 +3550,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559558</v>
+        <v>559711</v>
       </c>
       <c r="R28" t="n">
-        <v>7064251</v>
+        <v>7064112</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129404226</v>
+        <v>129403802</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559526</v>
+        <v>559558</v>
       </c>
       <c r="R29" t="n">
-        <v>7064261</v>
+        <v>7064251</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R30" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129403742</v>
+        <v>129410995</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,21 +3894,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559536</v>
+        <v>559567</v>
       </c>
       <c r="R31" t="n">
-        <v>7064197</v>
+        <v>7064280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,24 +3933,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,19 +3950,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129410976</v>
+        <v>129403742</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -4011,16 +3991,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559547</v>
+        <v>559536</v>
       </c>
       <c r="R32" t="n">
-        <v>7064246</v>
+        <v>7064197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,14 +4035,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,39 +4067,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410995</v>
+        <v>129410976</v>
       </c>
       <c r="B33" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559567</v>
+        <v>559547</v>
       </c>
       <c r="R33" t="n">
-        <v>7064280</v>
+        <v>7064246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4398,7 +4398,7 @@
         <v>129410991</v>
       </c>
       <c r="B36" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>129410964</v>
       </c>
       <c r="B37" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>129410989</v>
       </c>
       <c r="B38" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>129554321</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>129555462</v>
       </c>
       <c r="B43" t="n">
-        <v>90970</v>
+        <v>90975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B8" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,31 +1318,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1351,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R8" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1392,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,27 +1435,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R9" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1508,12 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,7 +1642,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410978</v>
+        <v>129403237</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1671,16 +1671,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559550</v>
+        <v>559726</v>
       </c>
       <c r="R11" t="n">
-        <v>7064229</v>
+        <v>7064107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,14 +1715,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,19 +1747,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B12" t="n">
         <v>57736</v>
@@ -1773,21 +1788,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R12" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,24 +1827,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,12 +1849,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403047</v>
+        <v>129410969</v>
       </c>
       <c r="B14" t="n">
         <v>57736</v>
@@ -2006,21 +2006,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559683</v>
+        <v>559580</v>
       </c>
       <c r="R14" t="n">
-        <v>7064133</v>
+        <v>7064207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,24 +2045,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,19 +2067,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410969</v>
+        <v>129403047</v>
       </c>
       <c r="B15" t="n">
         <v>57736</v>
@@ -2123,16 +2108,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559580</v>
+        <v>559683</v>
       </c>
       <c r="R15" t="n">
-        <v>7064207</v>
+        <v>7064133</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,14 +2152,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,19 +2184,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411002</v>
+        <v>129411003</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559393</v>
+        <v>559507</v>
       </c>
       <c r="R16" t="n">
-        <v>7064264</v>
+        <v>7064295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411003</v>
+        <v>129411002</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559507</v>
+        <v>559393</v>
       </c>
       <c r="R17" t="n">
-        <v>7064295</v>
+        <v>7064264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B20" t="n">
         <v>57736</v>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R20" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B21" t="n">
         <v>57736</v>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R21" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,27 +3287,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3316,13 +3325,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R26" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3351,7 +3360,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3361,12 +3370,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,10 +3397,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,36 +3408,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3442,13 +3437,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R27" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3477,7 +3472,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3482,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,7 +3514,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129403188</v>
+        <v>129403802</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3550,14 +3550,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559711</v>
+        <v>559558</v>
       </c>
       <c r="R28" t="n">
-        <v>7064112</v>
+        <v>7064251</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129403802</v>
+        <v>129403188</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559558</v>
+        <v>559711</v>
       </c>
       <c r="R29" t="n">
-        <v>7064251</v>
+        <v>7064112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129410995</v>
+        <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,16 +3894,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559567</v>
+        <v>559536</v>
       </c>
       <c r="R31" t="n">
-        <v>7064280</v>
+        <v>7064197</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,9 +3938,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,19 +3970,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129403742</v>
+        <v>129410976</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -3991,21 +4011,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559536</v>
+        <v>559547</v>
       </c>
       <c r="R32" t="n">
-        <v>7064197</v>
+        <v>7064246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,24 +4050,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,39 +4072,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410976</v>
+        <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559547</v>
+        <v>559567</v>
       </c>
       <c r="R33" t="n">
-        <v>7064246</v>
+        <v>7064280</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403648</v>
+        <v>129410968</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559588</v>
+        <v>559550</v>
       </c>
       <c r="R5" t="n">
-        <v>7064187</v>
+        <v>7064192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,19 +1086,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410968</v>
+        <v>129410965</v>
       </c>
       <c r="B6" t="n">
         <v>57736</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559550</v>
+        <v>559293</v>
       </c>
       <c r="R6" t="n">
-        <v>7064192</v>
+        <v>7064263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410965</v>
+        <v>129403648</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559293</v>
+        <v>559588</v>
       </c>
       <c r="R7" t="n">
-        <v>7064263</v>
+        <v>7064187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,14 +1268,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129410970</v>
+        <v>129406164</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,17 +1568,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559696</v>
+        <v>559539</v>
       </c>
       <c r="R10" t="n">
-        <v>7064169</v>
+        <v>7064245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,14 +1617,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,19 +1644,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129403237</v>
+        <v>129410970</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1671,21 +1685,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559726</v>
+        <v>559696</v>
       </c>
       <c r="R11" t="n">
-        <v>7064107</v>
+        <v>7064169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,24 +1724,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1861,27 +1860,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129406164</v>
+        <v>129403237</v>
       </c>
       <c r="B13" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1889,26 +1888,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559539</v>
+        <v>559726</v>
       </c>
       <c r="R13" t="n">
-        <v>7064245</v>
+        <v>7064107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1950,7 +1945,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B20" t="n">
         <v>57736</v>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R20" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B21" t="n">
         <v>57736</v>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R21" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410963</v>
+        <v>129410977</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559782</v>
+        <v>559545</v>
       </c>
       <c r="R22" t="n">
-        <v>7064120</v>
+        <v>7064246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410977</v>
+        <v>129410963</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,16 +2971,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2990,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559545</v>
+        <v>559782</v>
       </c>
       <c r="R23" t="n">
-        <v>7064246</v>
+        <v>7064120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,11 +3031,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3514,7 +3514,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129403802</v>
+        <v>129404226</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559558</v>
+        <v>559526</v>
       </c>
       <c r="R28" t="n">
-        <v>7064251</v>
+        <v>7064261</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129404226</v>
+        <v>129403802</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559526</v>
+        <v>559558</v>
       </c>
       <c r="R30" t="n">
-        <v>7064261</v>
+        <v>7064251</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129410968</v>
+        <v>129403648</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559550</v>
+        <v>559588</v>
       </c>
       <c r="R5" t="n">
-        <v>7064192</v>
+        <v>7064187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,14 +1064,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410965</v>
+        <v>129410968</v>
       </c>
       <c r="B6" t="n">
         <v>57736</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559293</v>
+        <v>559550</v>
       </c>
       <c r="R6" t="n">
-        <v>7064263</v>
+        <v>7064192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129403648</v>
+        <v>129410965</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559588</v>
+        <v>559293</v>
       </c>
       <c r="R7" t="n">
-        <v>7064187</v>
+        <v>7064263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,19 +1273,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,27 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R8" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,12 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B9" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,31 +1434,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R9" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1508,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,27 +1540,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129406164</v>
+        <v>129410970</v>
       </c>
       <c r="B10" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,26 +1568,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559539</v>
+        <v>559696</v>
       </c>
       <c r="R10" t="n">
-        <v>7064245</v>
+        <v>7064169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,19 +1608,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,19 +1630,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410970</v>
+        <v>129410978</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1691,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559696</v>
+        <v>559550</v>
       </c>
       <c r="R11" t="n">
-        <v>7064169</v>
+        <v>7064229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1717,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,7 +1744,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129410978</v>
+        <v>129403237</v>
       </c>
       <c r="B12" t="n">
         <v>57736</v>
@@ -1787,16 +1773,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559550</v>
+        <v>559726</v>
       </c>
       <c r="R12" t="n">
-        <v>7064229</v>
+        <v>7064107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,14 +1817,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,39 +1849,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129403237</v>
+        <v>129406164</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1888,22 +1889,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559726</v>
+        <v>559539</v>
       </c>
       <c r="R13" t="n">
-        <v>7064107</v>
+        <v>7064245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1940,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,12 +1950,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129410969</v>
+        <v>129403047</v>
       </c>
       <c r="B14" t="n">
         <v>57736</v>
@@ -2006,16 +2006,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559580</v>
+        <v>559683</v>
       </c>
       <c r="R14" t="n">
-        <v>7064207</v>
+        <v>7064133</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,14 +2050,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,19 +2082,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129403047</v>
+        <v>129410969</v>
       </c>
       <c r="B15" t="n">
         <v>57736</v>
@@ -2108,21 +2123,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559683</v>
+        <v>559580</v>
       </c>
       <c r="R15" t="n">
-        <v>7064133</v>
+        <v>7064207</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,24 +2162,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,19 +2184,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411003</v>
+        <v>129411002</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559507</v>
+        <v>559393</v>
       </c>
       <c r="R16" t="n">
-        <v>7064295</v>
+        <v>7064264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411002</v>
+        <v>129411003</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559393</v>
+        <v>559507</v>
       </c>
       <c r="R17" t="n">
-        <v>7064264</v>
+        <v>7064295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410977</v>
+        <v>129410963</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559545</v>
+        <v>559782</v>
       </c>
       <c r="R22" t="n">
-        <v>7064246</v>
+        <v>7064120</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,11 +2929,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410963</v>
+        <v>129410977</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2971,16 +2966,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2995,10 +2990,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559782</v>
+        <v>559545</v>
       </c>
       <c r="R23" t="n">
-        <v>7064120</v>
+        <v>7064246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,6 +3026,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129403742</v>
+        <v>129410995</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,21 +3894,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559536</v>
+        <v>559567</v>
       </c>
       <c r="R31" t="n">
-        <v>7064197</v>
+        <v>7064280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,24 +3933,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,19 +3950,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129410976</v>
+        <v>129403742</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -4011,16 +3991,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559547</v>
+        <v>559536</v>
       </c>
       <c r="R32" t="n">
-        <v>7064246</v>
+        <v>7064197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,14 +4035,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,39 +4067,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410995</v>
+        <v>129410976</v>
       </c>
       <c r="B33" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559567</v>
+        <v>559547</v>
       </c>
       <c r="R33" t="n">
-        <v>7064280</v>
+        <v>7064246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,37 +4906,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R41" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4965,7 +4970,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4975,7 +4980,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,42 +5018,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R42" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>129404125</v>
       </c>
       <c r="B8" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410963</v>
+        <v>129410977</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559782</v>
+        <v>559545</v>
       </c>
       <c r="R22" t="n">
-        <v>7064120</v>
+        <v>7064246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410977</v>
+        <v>129410963</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,16 +2971,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2990,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559545</v>
+        <v>559782</v>
       </c>
       <c r="R23" t="n">
-        <v>7064246</v>
+        <v>7064120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,11 +3031,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129402806</v>
+        <v>129402563</v>
       </c>
       <c r="B26" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,36 +3287,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3325,13 +3316,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559644</v>
+        <v>559610</v>
       </c>
       <c r="R26" t="n">
-        <v>7064145</v>
+        <v>7064096</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3360,7 +3351,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3361,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129402563</v>
+        <v>129402806</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,27 +3404,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3437,13 +3442,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559610</v>
+        <v>559644</v>
       </c>
       <c r="R27" t="n">
-        <v>7064096</v>
+        <v>7064145</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3472,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3482,12 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,7 +3514,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129404226</v>
+        <v>129403802</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559526</v>
+        <v>559558</v>
       </c>
       <c r="R28" t="n">
-        <v>7064261</v>
+        <v>7064251</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R29" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129403802</v>
+        <v>129403188</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559558</v>
+        <v>559711</v>
       </c>
       <c r="R30" t="n">
-        <v>7064251</v>
+        <v>7064112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129410995</v>
+        <v>129403742</v>
       </c>
       <c r="B31" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,16 +3894,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559567</v>
+        <v>559536</v>
       </c>
       <c r="R31" t="n">
-        <v>7064280</v>
+        <v>7064197</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,9 +3938,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,19 +3970,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129403742</v>
+        <v>129410976</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -3991,21 +4011,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559536</v>
+        <v>559547</v>
       </c>
       <c r="R32" t="n">
-        <v>7064197</v>
+        <v>7064246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,24 +4050,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,39 +4072,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410976</v>
+        <v>129410995</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559547</v>
+        <v>559567</v>
       </c>
       <c r="R33" t="n">
-        <v>7064246</v>
+        <v>7064280</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,42 +4906,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R41" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4970,7 +4965,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4980,7 +4975,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5007,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,37 +5013,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R42" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5117,7 @@
         <v>129555462</v>
       </c>
       <c r="B43" t="n">
-        <v>90975</v>
+        <v>90979</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129404125</v>
+        <v>129404504</v>
       </c>
       <c r="B8" t="n">
-        <v>91895</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,31 +1318,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1351,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559531</v>
+        <v>559488</v>
       </c>
       <c r="R8" t="n">
-        <v>7064282</v>
+        <v>7064261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1392,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129404504</v>
+        <v>129404125</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>91897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,27 +1435,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559488</v>
+        <v>559531</v>
       </c>
       <c r="R9" t="n">
-        <v>7064261</v>
+        <v>7064282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1508,12 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,7 +1642,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129410978</v>
+        <v>129403237</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1671,16 +1671,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559550</v>
+        <v>559726</v>
       </c>
       <c r="R11" t="n">
-        <v>7064229</v>
+        <v>7064107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,14 +1715,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,19 +1747,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129403237</v>
+        <v>129410978</v>
       </c>
       <c r="B12" t="n">
         <v>57736</v>
@@ -1773,21 +1788,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559726</v>
+        <v>559550</v>
       </c>
       <c r="R12" t="n">
-        <v>7064107</v>
+        <v>7064229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,24 +1827,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,12 +1849,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129403047</v>
+        <v>129410969</v>
       </c>
       <c r="B14" t="n">
         <v>57736</v>
@@ -2006,21 +2006,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559683</v>
+        <v>559580</v>
       </c>
       <c r="R14" t="n">
-        <v>7064133</v>
+        <v>7064207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,24 +2045,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,19 +2067,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410969</v>
+        <v>129403047</v>
       </c>
       <c r="B15" t="n">
         <v>57736</v>
@@ -2123,16 +2108,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559580</v>
+        <v>559683</v>
       </c>
       <c r="R15" t="n">
-        <v>7064207</v>
+        <v>7064133</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,14 +2152,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,22 +2184,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129411002</v>
+        <v>129402745</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,34 +2207,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559393</v>
+        <v>559641</v>
       </c>
       <c r="R16" t="n">
-        <v>7064264</v>
+        <v>7064141</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,9 +2269,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,22 +2301,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129411003</v>
+        <v>129402837</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,34 +2324,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559507</v>
+        <v>559663</v>
       </c>
       <c r="R17" t="n">
-        <v>7064295</v>
+        <v>7064138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,9 +2386,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,22 +2418,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129402745</v>
+        <v>129411002</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,39 +2441,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559641</v>
+        <v>559393</v>
       </c>
       <c r="R18" t="n">
-        <v>7064141</v>
+        <v>7064264</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,24 +2498,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2495,22 +2515,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129402837</v>
+        <v>129411003</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,39 +2538,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559663</v>
+        <v>559507</v>
       </c>
       <c r="R19" t="n">
-        <v>7064138</v>
+        <v>7064295</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,24 +2595,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,19 +2612,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129401699</v>
+        <v>129402491</v>
       </c>
       <c r="B20" t="n">
         <v>57736</v>
@@ -2655,7 +2655,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559667</v>
+        <v>559595</v>
       </c>
       <c r="R20" t="n">
-        <v>7064005</v>
+        <v>7064085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129402491</v>
+        <v>129401699</v>
       </c>
       <c r="B21" t="n">
         <v>57736</v>
@@ -2772,7 +2772,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559595</v>
+        <v>559667</v>
       </c>
       <c r="R21" t="n">
-        <v>7064085</v>
+        <v>7064005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410977</v>
+        <v>129410963</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559545</v>
+        <v>559782</v>
       </c>
       <c r="R22" t="n">
-        <v>7064246</v>
+        <v>7064120</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,11 +2929,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410963</v>
+        <v>129410977</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2971,16 +2966,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2995,10 +2990,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559782</v>
+        <v>559545</v>
       </c>
       <c r="R23" t="n">
-        <v>7064120</v>
+        <v>7064246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,6 +3026,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129404226</v>
+        <v>129403188</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559526</v>
+        <v>559711</v>
       </c>
       <c r="R29" t="n">
-        <v>7064261</v>
+        <v>7064112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129403188</v>
+        <v>129404226</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559711</v>
+        <v>559526</v>
       </c>
       <c r="R30" t="n">
-        <v>7064112</v>
+        <v>7064261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,27 +3865,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129403742</v>
+        <v>129410995</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3894,21 +3894,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559536</v>
+        <v>559567</v>
       </c>
       <c r="R31" t="n">
-        <v>7064197</v>
+        <v>7064280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,24 +3933,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,19 +3950,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129410976</v>
+        <v>129403742</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -4011,16 +3991,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559547</v>
+        <v>559536</v>
       </c>
       <c r="R32" t="n">
-        <v>7064246</v>
+        <v>7064197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,14 +4035,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,39 +4067,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129410995</v>
+        <v>129410976</v>
       </c>
       <c r="B33" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559567</v>
+        <v>559547</v>
       </c>
       <c r="R33" t="n">
-        <v>7064280</v>
+        <v>7064246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,37 +4906,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R41" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4965,7 +4970,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4975,7 +4980,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,42 +5018,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R42" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5117,7 @@
         <v>129555462</v>
       </c>
       <c r="B43" t="n">
-        <v>90979</v>
+        <v>90981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 30962-2025 artfynd.xlsx
+++ b/artfynd/A 30962-2025 artfynd.xlsx
@@ -4689,7 +4689,7 @@
         <v>129554412</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>129555537</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129554691</v>
+        <v>129554321</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,42 +4906,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559654</v>
+        <v>559681</v>
       </c>
       <c r="R41" t="n">
-        <v>7064439</v>
+        <v>7064349</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4970,7 +4965,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4980,7 +4975,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5007,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129554321</v>
+        <v>129554691</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,37 +5013,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>559681</v>
+        <v>559654</v>
       </c>
       <c r="R42" t="n">
-        <v>7064349</v>
+        <v>7064439</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5117,7 @@
         <v>129555462</v>
       </c>
       <c r="B43" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
